--- a/Design/Data_Templates/SEMS_Applicant_Import_Mapping_Specification.xlsx
+++ b/Design/Data_Templates/SEMS_Applicant_Import_Mapping_Specification.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="R8f4440f7598f4656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_COLUMN_MAPPING" sheetId="2" r:id="R97c2157b532a498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_ERROR_CODES" sheetId="3" r:id="Ra564dac0249d420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ROW_RULES" sheetId="4" r:id="R5ff0d77ca5514789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_IMPORT_FLOW" sheetId="5" r:id="R1d89726e0b204528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_TEST_CASES" sheetId="6" r:id="R14b51e000e3a4de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_OPEN_DECISIONS" sheetId="7" r:id="Rc7d671e3d5cd45c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="1" r:id="Rc5bc45df971841b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_COLUMN_MAPPING" sheetId="2" r:id="R7d53d51c578f48b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_ERROR_CODES" sheetId="3" r:id="R44edb82b02154752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ROW_RULES" sheetId="4" r:id="R0c8941a17eff4e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_IMPORT_FLOW" sheetId="5" r:id="Rac715fdc5cb34663"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_TEST_CASES" sheetId="6" r:id="R4990214d520d4548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_OPEN_DECISIONS" sheetId="7" r:id="R59afe01666be4a3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,21 +143,21 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F1FB"/>
         </x:patternFill>
       </x:fill>
@@ -167,21 +167,21 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -191,7 +191,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -201,7 +201,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -337,9 +337,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -536,13 +536,13 @@
         <x:v>Business Key</x:v>
       </x:c>
       <x:c r="B8" s="22" t="str">
-        <x:v>round_id + student_id</x:v>
+        <x:v>round_id + scholarship_type_id + student_id</x:v>
       </x:c>
       <x:c r="C8" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
       <x:c r="D8" s="22" t="str">
-        <x:v>หากหนึ่งคนสมัครหลายประเภททุนในรอบเดียว ต้องเพิ่ม scholarship_type_id</x:v>
+        <x:v>Supports multiple scholarship types in one round</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -550,10 +550,10 @@
         <x:v>Hard Required Draft</x:v>
       </x:c>
       <x:c r="B9" s="22" t="str">
-        <x:v>student_id, first_name, last_name, faculty_name, major_name, year_level</x:v>
+        <x:v>Faculty / Program / Field required before Evaluation</x:v>
       </x:c>
       <x:c r="C9" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
       <x:c r="D9" s="22" t="str">
         <x:v>title/application_date/gpa เป็น Provisional ตาม Data Dictionary ปัจจุบัน</x:v>
@@ -604,10 +604,10 @@
         <x:v>Duplicate Rule</x:v>
       </x:c>
       <x:c r="B13" s="22" t="str">
-        <x:v>ซ้ำในไฟล์ = Error; ซ้ำกับรอบ = Default Skip; Update แบบมีเงื่อนไข</x:v>
+        <x:v>Duplicate in file = Error; duplicate in database = Skip; never upsert; resolve before Evaluation</x:v>
       </x:c>
       <x:c r="C13" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
       <x:c r="D13" s="22" t="str">
         <x:v>ห้าม Update หลังเริ่ม Evaluation</x:v>
@@ -618,10 +618,10 @@
         <x:v>Timezone</x:v>
       </x:c>
       <x:c r="B14" s="22" t="str">
-        <x:v>Asia/Bangkok</x:v>
+        <x:v>Asia/Bangkok; ISO codes where available; documented legacy normalization</x:v>
       </x:c>
       <x:c r="C14" s="22" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
       <x:c r="D14" s="22" t="str">
         <x:v>แปลงปี พ.ศ. เป็น ค.ศ. ก่อนเก็บ</x:v>
@@ -2113,7 +2113,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R211c6368960a4ac2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ff9440cf172406e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2844,7 +2844,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5272fd58aace48b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d9fd443ff414bde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2965,7 +2965,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46162f83283b434b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1012a914c37b4653"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3137,7 +3137,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra375f260013c4966"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3efad80f7bb34159"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3379,7 +3379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1846fedc0ba64fa1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45838870ccf3496e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3420,13 +3420,13 @@
         <x:v>Business Key เมื่อหนึ่งคนสมัครหลายประเภททุนในรอบเดียว</x:v>
       </x:c>
       <x:c r="C2" s="22" t="str">
-        <x:v>Draft ใช้ round_id + student_id</x:v>
+        <x:v>Confirmed: round_id + scholarship_type_id + student_id</x:v>
       </x:c>
       <x:c r="D2" s="22" t="str">
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="E2" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3437,13 +3437,13 @@
         <x:v>จะรองรับ Legacy Continuation Row ถึงเมื่อใด</x:v>
       </x:c>
       <x:c r="C3" s="22" t="str">
-        <x:v>Template ใหม่แยก Sheet; Legacy รองรับช่วงเปลี่ยนผ่าน</x:v>
+        <x:v>Confirmed: measure in UAT and first production cycle</x:v>
       </x:c>
       <x:c r="D3" s="22" t="str">
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="E3" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3454,13 +3454,13 @@
         <x:v>Duplicate กับข้อมูลเดิม Update ได้หรือไม่</x:v>
       </x:c>
       <x:c r="C4" s="22" t="str">
-        <x:v>Default Skip; Update เฉพาะผู้ดูแลเลือกและยังไม่มี Evaluation</x:v>
+        <x:v>Confirmed: file duplicate Error; database duplicate Skip; never upsert; explicitly resolve before Evaluation</x:v>
       </x:c>
       <x:c r="D4" s="22" t="str">
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="E4" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3471,13 +3471,13 @@
         <x:v>รายการ Hard Required / Required before Evaluation สุดท้าย</x:v>
       </x:c>
       <x:c r="C5" s="22" t="str">
-        <x:v>Hard Required 6 ฟิลด์; title/date/GPA เป็น Provisional</x:v>
+        <x:v>Confirmed: Faculty / Program / Field</x:v>
       </x:c>
       <x:c r="D5" s="22" t="str">
         <x:v>งานทุน/ผู้ประเมิน</x:v>
       </x:c>
       <x:c r="E5" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3488,13 +3488,13 @@
         <x:v>รูปแบบวันที่/โทรศัพท์ที่รองรับอย่างเป็นทางการ</x:v>
       </x:c>
       <x:c r="C6" s="22" t="str">
-        <x:v>Template ISO; Legacy parser เฉพาะรูปแบบที่ประกาศ</x:v>
+        <x:v>Confirmed: ISO code where available; normalize documented legacy values</x:v>
       </x:c>
       <x:c r="D6" s="22" t="str">
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="E6" s="22" t="str">
-        <x:v>Pending Confirmation</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3505,13 +3505,13 @@
         <x:v>ค่าอุปกรณ์การศึกษาเป็นต่อเดือน/ภาค/ปี</x:v>
       </x:c>
       <x:c r="C7" s="22" t="str">
-        <x:v>เพิ่ม expense_period ใน Template ใหม่</x:v>
+        <x:v>Confirmed: education material cost is per semester</x:v>
       </x:c>
       <x:c r="D7" s="22" t="str">
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="E7" s="22" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3522,13 +3522,13 @@
         <x:v>Reference Values ทางการ</x:v>
       </x:c>
       <x:c r="C8" s="22" t="str">
-        <x:v>อนุมัติ Code List สำหรับที่พัก สถานะครอบครัว ผู้จ่ายค่าเรียน อาชีพ</x:v>
+        <x:v>Confirmed: database-backed, versioned effective-dated code lists</x:v>
       </x:c>
       <x:c r="D8" s="22" t="str">
         <x:v>งานทุน</x:v>
       </x:c>
       <x:c r="E8" s="22" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3539,13 +3539,13 @@
         <x:v>ประวัติ กยศ./ทุนเป็นระดับ Applicant หรือ Snapshot ต่อรอบ</x:v>
       </x:c>
       <x:c r="C9" s="22" t="str">
-        <x:v>เก็บระดับ Applicant พร้อม source import; ต้องยืนยัน</x:v>
+        <x:v>Confirmed: validation snapshot stored per application</x:v>
       </x:c>
       <x:c r="D9" s="22" t="str">
         <x:v>งานทุน/ทีมพัฒนา</x:v>
       </x:c>
       <x:c r="E9" s="22" t="str">
-        <x:v>Open</x:v>
+        <x:v>Confirmed Response — Pending Formal Approval</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3559,7 +3559,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33afe19c17904e99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f984f78e6a64e87"/>
   </x:tableParts>
 </x:worksheet>
 </file>